--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484858_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484858_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. GALVEZ ARROYO</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6405</v>
+        <v>3.9043</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2787</v>
+        <v>1.5385</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3618</v>
+        <v>2.3658</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4661</v>
+        <v>4.0483</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3922</v>
+        <v>0.7403</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0739</v>
+        <v>3.308</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5825</v>
+        <v>3.5636</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4267</v>
+        <v>1.49</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1558</v>
+        <v>2.0735</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1163</v>
+        <v>0.4847</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0344</v>
+        <v>-0.7497</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0819</v>
+        <v>1.2344</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1322</v>
+        <v>-1.3209</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2079</v>
+        <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0535</v>
+        <v>-1.0386</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2438</v>
+        <v>-0.7042</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1904</v>
+        <v>-0.3344</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0452</v>
+        <v>-0.2377</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5846</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5395</v>
+        <v>-0.2377</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>V. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6384</v>
+        <v>3.6675</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2462</v>
+        <v>2.5967</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3922</v>
+        <v>1.0708</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0483</v>
+        <v>2.4661</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7403</v>
+        <v>1.3922</v>
       </c>
       <c r="I3" t="n">
-        <v>3.308</v>
+        <v>1.0739</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5636</v>
+        <v>3.5825</v>
       </c>
       <c r="K3" t="n">
-        <v>1.49</v>
+        <v>1.4267</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0735</v>
+        <v>2.1558</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4847</v>
+        <v>-1.1163</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7497</v>
+        <v>-0.0344</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2344</v>
+        <v>-1.0819</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1322</v>
+        <v>2.0757</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3209</v>
+        <v>-1.1322</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4531</v>
+        <v>3.2079</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3044</v>
+        <v>-0.9195</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-0.4382</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3079</v>
+        <v>-0.4814</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2377</v>
+        <v>0.0452</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5846</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2377</v>
+        <v>-0.5395</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.5057</v>
+        <v>-1.2483</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2683</v>
+        <v>0.1214</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2374</v>
+        <v>-1.3697</v>
       </c>
       <c r="G4" t="n">
         <v>1.3751</v>
@@ -766,13 +766,13 @@
         <v>3.2079</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.2844</v>
+        <v>-2.0269</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2904</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9939</v>
+        <v>-1.1262</v>
       </c>
       <c r="V4" t="n">
         <v>0.347</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>A. ORTIN GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1525</v>
+        <v>-1.9926</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3893</v>
+        <v>-1.5564</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2367</v>
+        <v>-0.4362</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1496</v>
+        <v>-0.5504</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1299</v>
+        <v>-0.6934</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0197</v>
+        <v>0.143</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.09370000000000001</v>
+        <v>0.2527</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2426</v>
+        <v>0.1534</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1489</v>
+        <v>0.0993</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.056</v>
+        <v>-0.8031</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1127</v>
+        <v>-0.8467</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1687</v>
+        <v>0.0437</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R5" t="n">
-        <v>1.887</v>
+        <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3427</v>
+        <v>-0.9326</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4086</v>
+        <v>-0.356</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9341</v>
+        <v>-0.5766</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3398</v>
+        <v>0.6226</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ORTIN GOMEZ</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.7359</v>
+        <v>-2.1803</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.141</v>
+        <v>-2.6816</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5949</v>
+        <v>0.5013</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5504</v>
+        <v>-1.1496</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6934</v>
+        <v>-0.1299</v>
       </c>
       <c r="I6" t="n">
-        <v>0.143</v>
+        <v>-1.0197</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2527</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1534</v>
+        <v>-0.2426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0993</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8031</v>
+        <v>-1.056</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8467</v>
+        <v>0.1127</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0437</v>
+        <v>-1.1687</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0757</v>
+        <v>-1.887</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9435</v>
+        <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6759</v>
+        <v>-1.3704</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9406</v>
+        <v>-0.7009</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7353</v>
+        <v>-0.6695</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6226</v>
+        <v>0.3398</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>I. DURAN OLMOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1152</v>
+        <v>-3.3704</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4497</v>
+        <v>-0.873</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6654</v>
+        <v>-2.4974</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1055</v>
+        <v>-1.3189</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9848</v>
+        <v>0.5776</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8793</v>
+        <v>-1.8965</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4786</v>
+        <v>-0.4257</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1538</v>
+        <v>0.0423</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6323</v>
+        <v>-0.468</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5841</v>
+        <v>-0.8932</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8310999999999999</v>
+        <v>0.5353</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.753</v>
+        <v>-1.4285</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.1514</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7148</v>
+        <v>-0.7123</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2294</v>
+        <v>-0.4473</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4855</v>
+        <v>-0.2651</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5922</v>
+        <v>-3.4148</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4524</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8603</v>
+        <v>-3.4148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. DURAN OLMOS</t>
+          <t>N. ALBALADEJO PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.4052</v>
+        <v>-3.7078</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7756</v>
+        <v>-4.0374</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6297</v>
+        <v>0.3296</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3189</v>
+        <v>-3.0937</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5776</v>
+        <v>-2.1733</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8965</v>
+        <v>-0.9204</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4257</v>
+        <v>-2.3063</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0423</v>
+        <v>-1.0824</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.468</v>
+        <v>-1.2239</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8932</v>
+        <v>-0.7874</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5353</v>
+        <v>-1.0909</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4285</v>
+        <v>0.3035</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0757</v>
+        <v>0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7472</v>
+        <v>-1.2443</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3498</v>
+        <v>-0.4103</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3974</v>
+        <v>-0.8341</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.4148</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.4148</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. ALBALADEJO PEREZ</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2382</v>
+        <v>-3.9462</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3297</v>
+        <v>-1.9369</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0916</v>
+        <v>-2.0093</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0937</v>
+        <v>-2.1055</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1733</v>
+        <v>-2.9848</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9204</v>
+        <v>0.8793</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3063</v>
+        <v>0.4786</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0824</v>
+        <v>-2.1538</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2239</v>
+        <v>2.6323</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7874</v>
+        <v>-2.5841</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0909</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3035</v>
+        <v>-1.753</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5661</v>
+        <v>-1.887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3209</v>
+        <v>-4.1514</v>
       </c>
       <c r="R9" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7747</v>
+        <v>-1.5459</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7026</v>
+        <v>-0.7165</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0722</v>
+        <v>-0.8294</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06419999999999999</v>
+        <v>1.5922</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.4524</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="10">
@@ -1192,10 +1192,10 @@
         <v>-8.873799999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.8287</v>
+        <v>-6.828700000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.045100000000001</v>
+        <v>-2.045099999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3285999999999998</v>
@@ -1207,7 +1207,7 @@
         <v>3.2479</v>
       </c>
       <c r="J10" t="n">
-        <v>8.0746</v>
+        <v>8.074600000000002</v>
       </c>
       <c r="K10" t="n">
         <v>-0.1488999999999998</v>
@@ -1222,7 +1222,7 @@
         <v>-3.4275</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.9755</v>
+        <v>-4.975499999999999</v>
       </c>
       <c r="P10" t="n">
         <v>1.887</v>
@@ -1234,16 +1234,16 @@
         <v>17.9265</v>
       </c>
       <c r="S10" t="n">
-        <v>-9.7906</v>
+        <v>-9.7905</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.6741</v>
+        <v>-4.674099999999999</v>
       </c>
       <c r="U10" t="n">
         <v>-5.1167</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6414999999999997</v>
+        <v>-0.6415000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>5.8102</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.6931</v>
+        <v>6.5498</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1376</v>
+        <v>4.6504</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5555</v>
+        <v>1.8994</v>
       </c>
       <c r="G11" t="n">
         <v>2.9306</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6684</v>
+        <v>0.5251</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8905</v>
+        <v>0.4033</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2222</v>
+        <v>0.1218</v>
       </c>
       <c r="V11" t="n">
         <v>2.1506</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.4916</v>
+        <v>2.4921</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1593</v>
+        <v>1.4773</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3322</v>
+        <v>1.0148</v>
       </c>
       <c r="G12" t="n">
         <v>1.8241</v>
@@ -1390,13 +1390,13 @@
         <v>1.6983</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2902</v>
+        <v>2.2907</v>
       </c>
       <c r="T12" t="n">
-        <v>1.67</v>
+        <v>0.9879</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6202</v>
+        <v>1.3028</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3018</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>C. SEGUI HEREDIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5476</v>
+        <v>2.2039</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1638</v>
+        <v>0.4176</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3838</v>
+        <v>1.7863</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4781</v>
+        <v>1.3623</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9416</v>
+        <v>3.3651</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4635</v>
+        <v>-2.0029</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2145</v>
+        <v>2.5325</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4143</v>
+        <v>3.7564</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2239</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2637</v>
+        <v>-1.1702</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4727</v>
+        <v>-0.3913</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7363</v>
+        <v>-0.7789</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2644</v>
+        <v>-3.0192</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-4.9062</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9746</v>
+        <v>1.3704</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9493</v>
+        <v>0.3199</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0253</v>
+        <v>1.0506</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1696</v>
+        <v>2.4904</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.4714</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1696</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2369</v>
+        <v>2.1398</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9025</v>
+        <v>1.6766</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6656</v>
+        <v>0.4632</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7388</v>
+        <v>1.4781</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9316</v>
+        <v>1.9416</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1928</v>
+        <v>-0.4635</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1371</v>
+        <v>1.2145</v>
       </c>
       <c r="K14" t="n">
-        <v>2.689</v>
+        <v>2.4143</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4481</v>
+        <v>-1.1998</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3982</v>
+        <v>0.2637</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2426</v>
+        <v>-0.4727</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.6408</v>
+        <v>0.7363</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3209</v>
+        <v>2.2644</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7548</v>
+        <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4226</v>
+        <v>0.5668</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.4621</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5814</v>
+        <v>0.1047</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6036</v>
+        <v>-2.1696</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6036</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2344</v>
+        <v>1.2272</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5464</v>
+        <v>2.7076</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6879999999999999</v>
+        <v>-1.4804</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.1775</v>
+        <v>1.7388</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8313</v>
+        <v>2.9316</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3462</v>
+        <v>-1.1928</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2176</v>
+        <v>4.1371</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.1224</v>
+        <v>2.689</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9049</v>
+        <v>1.4481</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.96</v>
+        <v>-2.3982</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2911</v>
+        <v>0.2426</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2511</v>
+        <v>-2.6408</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9435</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.0757</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1102</v>
+        <v>1.4129</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6135</v>
+        <v>0.6463</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4968</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2452</v>
+        <v>-0.6036</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.019</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. SEGUI HEREDIA</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9734</v>
+        <v>1.2138</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6542</v>
+        <v>0.1381</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6276</v>
+        <v>1.0757</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3623</v>
+        <v>0.329</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3651</v>
+        <v>0.3506</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0029</v>
+        <v>-0.0216</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5325</v>
+        <v>0.0423</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7564</v>
+        <v>0.0423</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1702</v>
+        <v>0.2868</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3913</v>
+        <v>0.3083</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7789</v>
+        <v>-0.0216</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.0192</v>
+        <v>0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.9062</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.887</v>
+        <v>0.7548</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1399</v>
+        <v>0.1299</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7519</v>
+        <v>0.0958</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8918</v>
+        <v>0.0341</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4714</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.824</v>
+        <v>0.6885</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2517</v>
+        <v>1.2671</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0757</v>
+        <v>-0.5786</v>
       </c>
       <c r="G17" t="n">
-        <v>0.329</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3506</v>
+        <v>-0.4915</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0216</v>
+        <v>-0.013</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0423</v>
+        <v>0.9579</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0423</v>
+        <v>0.1268</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2868</v>
+        <v>-1.4624</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3083</v>
+        <v>-0.6182</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0216</v>
+        <v>-0.8442</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7548</v>
+        <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2598</v>
+        <v>0.9852</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2939</v>
+        <v>0.4979</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0341</v>
+        <v>0.4874</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0678</v>
+        <v>-0.7297</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4876</v>
+        <v>-0.9151</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4198</v>
+        <v>0.1853</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-3.1775</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4915</v>
+        <v>-1.8313</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.013</v>
+        <v>-1.3462</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9579</v>
+        <v>-1.2176</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1268</v>
+        <v>-2.1224</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.9049</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4624</v>
+        <v>-1.96</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6182</v>
+        <v>0.2911</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8442</v>
+        <v>-2.2511</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.9435</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2.0757</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.1322</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.1887</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.3209</v>
-      </c>
       <c r="S19" t="n">
-        <v>0.3645</v>
+        <v>2.1461</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2816</v>
+        <v>1.152</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6461</v>
+        <v>0.9941</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9244</v>
+        <v>1.2452</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9244</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VAICIUNAS</t>
+          <t>J. GARCIA CORBI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.151</v>
+        <v>-1.0232</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5392</v>
+        <v>-1.9327</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3882</v>
+        <v>0.9095</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6906</v>
+        <v>-0.7579</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.8596</v>
+        <v>0.3506</v>
       </c>
       <c r="I20" t="n">
-        <v>0.169</v>
+        <v>-1.1085</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9542</v>
+        <v>-1.1903</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.3869</v>
+        <v>0.0266</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5673</v>
+        <v>-1.2169</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2637</v>
+        <v>0.4324</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4727</v>
+        <v>0.324</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7363</v>
+        <v>0.1083</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3209</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2644</v>
+        <v>0.7548</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2187</v>
+        <v>-0.0766</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3585</v>
+        <v>-0.1007</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1398</v>
+        <v>0.0241</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GARCIA CORBI</t>
+          <t>A. VAICIUNAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4839</v>
+        <v>-1.1245</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4198</v>
+        <v>-3.5392</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9359</v>
+        <v>2.4147</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7579</v>
+        <v>-2.6906</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3506</v>
+        <v>-2.8596</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1085</v>
+        <v>0.169</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1903</v>
+        <v>-2.9542</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0266</v>
+        <v>-2.3869</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2169</v>
+        <v>-0.5673</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4324</v>
+        <v>0.2637</v>
       </c>
       <c r="N21" t="n">
-        <v>0.324</v>
+        <v>-0.4727</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1083</v>
+        <v>0.7363</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7548</v>
+        <v>2.2644</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5373</v>
+        <v>0.2451</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5879</v>
+        <v>0.3585</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0506</v>
+        <v>-0.1134</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1769</v>
+        <v>-5.3807</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1042</v>
+        <v>-4.5196</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0728</v>
+        <v>-0.8611</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8208</v>
@@ -2170,13 +2170,13 @@
         <v>1.3209</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6014</v>
+        <v>0.1949</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.291</v>
+        <v>0.2936</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3103</v>
+        <v>-0.0987</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2452</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.874000000000001</v>
+        <v>8.874000000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>2.045099999999999</v>
+        <v>2.045100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>6.8287</v>
+        <v>6.828799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0.3285999999999989</v>
@@ -2218,19 +2218,19 @@
         <v>3.5764</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.2478</v>
+        <v>-3.247800000000001</v>
       </c>
       <c r="J23" t="n">
         <v>8.4033</v>
       </c>
       <c r="K23" t="n">
-        <v>3.427700000000001</v>
+        <v>3.4277</v>
       </c>
       <c r="L23" t="n">
         <v>4.975599999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.074399999999999</v>
+        <v>-8.074400000000001</v>
       </c>
       <c r="N23" t="n">
         <v>0.1488000000000002</v>
@@ -2248,13 +2248,13 @@
         <v>16.0395</v>
       </c>
       <c r="S23" t="n">
-        <v>9.7906</v>
+        <v>9.790500000000002</v>
       </c>
       <c r="T23" t="n">
-        <v>5.1167</v>
+        <v>5.1166</v>
       </c>
       <c r="U23" t="n">
-        <v>4.674</v>
+        <v>4.674099999999999</v>
       </c>
       <c r="V23" t="n">
         <v>0.6415999999999999</v>
@@ -2263,7 +2263,7 @@
         <v>6.4518</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.8102</v>
+        <v>-5.810199999999999</v>
       </c>
     </row>
   </sheetData>
